--- a/analysis_steps.xlsx
+++ b/analysis_steps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestFolderSJ\mt_lion_crossings_and_corridors\mt_lion_crossings_and_corridors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://egretorg-my.sharepoint.com/personal/scott_jennings_egret_org/Documents/Projects/other_research/mt_lion_crossings_and_corridors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6998644D-BCD5-4449-8257-06DBCE91F9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{6998644D-BCD5-4449-8257-06DBCE91F9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5D345CC-B35B-455A-81AE-7113515933C6}"/>
   <bookViews>
-    <workbookView xWindow="31020" yWindow="105" windowWidth="19515" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="0" windowWidth="19190" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>notes</t>
   </si>
@@ -63,9 +63,6 @@
     <t>do UD look ok for big movement/dispersing lions?</t>
   </si>
   <si>
-    <t>any lions to exclude based on UD quirks?</t>
-  </si>
-  <si>
     <t>check naïve crossings for all lions with OK UD</t>
   </si>
   <si>
@@ -78,9 +75,6 @@
     <t>how many crossings per lion</t>
   </si>
   <si>
-    <t>any lions to exclude for too few crossings? Might decide not to exclude any for this reason; double check used vs available</t>
-  </si>
-  <si>
     <t>extract segment habitat, etc. for segments in new UD</t>
   </si>
   <si>
@@ -127,6 +121,51 @@
   </si>
   <si>
     <t>sort out git commits/ignore between C and E</t>
+  </si>
+  <si>
+    <t>decided to fill holes</t>
+  </si>
+  <si>
+    <t>yup</t>
+  </si>
+  <si>
+    <t>any lions to exclude based on UD quirks? Yes, excluding P34 for quirky home range and few overall fixes/days tracked</t>
+  </si>
+  <si>
+    <t>all good except P30 who only had crossings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any lions to exclude for too few crossings? The ratio of crossing steps to total steps is fairly similar between lions with few and lots of crossings, so might not to exclude any for this reason; double check used vs available. </t>
+  </si>
+  <si>
+    <t>get road segments for new UD</t>
+  </si>
+  <si>
+    <t>more lions = more area = more segments</t>
+  </si>
+  <si>
+    <t>get BBMM whole segments</t>
+  </si>
+  <si>
+    <t>this should be one segment per BBMM</t>
+  </si>
+  <si>
+    <t>tre+shr</t>
+  </si>
+  <si>
+    <t>impervious</t>
+  </si>
+  <si>
+    <t>calculate cohesion</t>
+  </si>
+  <si>
+    <t>riparian intersections</t>
+  </si>
+  <si>
+    <t>bridges</t>
+  </si>
+  <si>
+    <t>class</t>
   </si>
 </sst>
 </file>
@@ -142,7 +181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +212,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -186,15 +231,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,20 +519,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
       <c r="C1" t="s">
@@ -499,176 +543,279 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>45895</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="7"/>
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="5">
+        <v>45896</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>34</v>
+      </c>
+      <c r="D4" s="5">
+        <v>45897</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
+      <c r="D5" s="5">
+        <v>45897</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>8</v>
       </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="5">
+        <v>45897</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
+      <c r="D7" s="5">
+        <v>45897</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
+      <c r="D8" s="5">
+        <v>45897</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45898</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5">
+        <v>45898</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="5">
+        <v>45898</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="5">
+        <v>45898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="5">
+        <v>45898</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="5">
+        <v>45899</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="B30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/analysis_steps.xlsx
+++ b/analysis_steps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://egretorg-my.sharepoint.com/personal/scott_jennings_egret_org/Documents/Projects/other_research/mt_lion_crossings_and_corridors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{6998644D-BCD5-4449-8257-06DBCE91F9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5D345CC-B35B-455A-81AE-7113515933C6}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{6998644D-BCD5-4449-8257-06DBCE91F9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DED1A9-5A30-412F-94D4-7AB3536699AE}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="0" windowWidth="19190" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -710,6 +710,9 @@
       <c r="B15" t="s">
         <v>42</v>
       </c>
+      <c r="D15" s="5">
+        <v>45902</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
@@ -717,6 +720,9 @@
       </c>
       <c r="B16" t="s">
         <v>43</v>
+      </c>
+      <c r="D16" s="5">
+        <v>45901</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
